--- a/artfynd/A 17267-2026 artfynd.xlsx
+++ b/artfynd/A 17267-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY52"/>
+  <dimension ref="A1:AY54"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,14 +675,14 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>133315969</v>
+        <v>133315961</v>
       </c>
       <c r="B2" t="n">
-        <v>79358</v>
+        <v>79373</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
@@ -713,10 +713,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>495692</v>
+        <v>495698</v>
       </c>
       <c r="R2" t="n">
-        <v>7037757</v>
+        <v>7037606</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -743,12 +743,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-24</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-24</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -763,7 +763,7 @@
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AJ2" t="inlineStr">
@@ -776,14 +776,9 @@
           <t>Picea abies</t>
         </is>
       </c>
-      <c r="AM2" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr"/>
@@ -801,10 +796,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>133315948</v>
+        <v>133315962</v>
       </c>
       <c r="B3" t="n">
-        <v>99178</v>
+        <v>79373</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -812,39 +807,26 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="L3" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -852,10 +834,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>495621</v>
+        <v>495710</v>
       </c>
       <c r="R3" t="n">
-        <v>7037632</v>
+        <v>7037634</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -882,17 +864,17 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-24</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-24</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Minst 4 plantor inom ca 0,5 m2 yta.</t>
+          <t>På grenar av en stående död gran och även på andra levande granar.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -908,6 +890,26 @@
       <c r="AH3" t="inlineStr">
         <is>
           <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ3" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK3" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM3" t="inlineStr">
+        <is>
+          <t>Stående död trädstam/högstubbe</t>
+        </is>
+      </c>
+      <c r="AO3" t="inlineStr">
+        <is>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr"/>
@@ -925,32 +927,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>133315934</v>
+        <v>133315963</v>
       </c>
       <c r="B4" t="n">
-        <v>80473</v>
+        <v>79373</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -963,10 +965,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>495732</v>
+        <v>495696</v>
       </c>
       <c r="R4" t="n">
-        <v>7037736</v>
+        <v>7037705</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1003,7 +1005,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>På en sälglåga.</t>
+          <t>På flera granar.</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1018,27 +1020,22 @@
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM4" t="inlineStr">
-        <is>
-          <t>Bark på dött träd</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>Bark of dead wood # Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr"/>
@@ -1056,14 +1053,14 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>133315967</v>
+        <v>133315964</v>
       </c>
       <c r="B5" t="n">
-        <v>79358</v>
+        <v>79373</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
@@ -1094,10 +1091,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>495759</v>
+        <v>495652</v>
       </c>
       <c r="R5" t="n">
-        <v>7037725</v>
+        <v>7037696</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1149,7 +1146,7 @@
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AJ5" t="inlineStr">
@@ -1162,14 +1159,9 @@
           <t>Picea abies</t>
         </is>
       </c>
-      <c r="AM5" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr"/>
@@ -1187,41 +1179,37 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>133315941</v>
+        <v>133315965</v>
       </c>
       <c r="B6" t="n">
-        <v>80485</v>
+        <v>79373</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6464</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="J6" t="inlineStr"/>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
+      <c r="K6" t="inlineStr"/>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1229,10 +1217,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>495733</v>
+        <v>495666</v>
       </c>
       <c r="R6" t="n">
-        <v>7037737</v>
+        <v>7037645</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1269,7 +1257,7 @@
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>På en sälglåga.</t>
+          <t>På flera granar.</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1287,24 +1275,24 @@
           <t>Barrskog</t>
         </is>
       </c>
+      <c r="AI6" t="inlineStr">
+        <is>
+          <t>Barrblandskog.</t>
+        </is>
+      </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM6" t="inlineStr">
-        <is>
-          <t>Bark på dött träd</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>Bark of dead wood # Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr"/>
@@ -1322,14 +1310,14 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>133315961</v>
+        <v>133315966</v>
       </c>
       <c r="B7" t="n">
-        <v>79358</v>
+        <v>79373</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
@@ -1360,10 +1348,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>495698</v>
+        <v>495747</v>
       </c>
       <c r="R7" t="n">
-        <v>7037606</v>
+        <v>7037681</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1390,12 +1378,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1443,41 +1431,37 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>133315939</v>
+        <v>133315967</v>
       </c>
       <c r="B8" t="n">
-        <v>80473</v>
+        <v>79373</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="J8" t="inlineStr"/>
-      <c r="K8" t="inlineStr">
-        <is>
-          <t>med soral</t>
-        </is>
-      </c>
+      <c r="K8" t="inlineStr"/>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
@@ -1485,10 +1469,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>495555</v>
+        <v>495759</v>
       </c>
       <c r="R8" t="n">
-        <v>7037564</v>
+        <v>7037725</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1525,7 +1509,7 @@
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>På sälg med soral.</t>
+          <t>På flera granar.</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1540,27 +1524,27 @@
       </c>
       <c r="AH8" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM8" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr"/>
@@ -1578,41 +1562,37 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>133315940</v>
+        <v>133315968</v>
       </c>
       <c r="B9" t="n">
-        <v>80485</v>
+        <v>79373</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6464</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="J9" t="inlineStr"/>
-      <c r="K9" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
+      <c r="K9" t="inlineStr"/>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
@@ -1620,10 +1600,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>495734</v>
+        <v>495723</v>
       </c>
       <c r="R9" t="n">
-        <v>7037731</v>
+        <v>7037735</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1658,11 +1638,6 @@
           <t>2026-04-23</t>
         </is>
       </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>På en rönn.</t>
-        </is>
-      </c>
       <c r="AD9" t="b">
         <v>0</v>
       </c>
@@ -1680,22 +1655,17 @@
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>rönn</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>Sorbus aucuparia</t>
-        </is>
-      </c>
-      <c r="AM9" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Sorbus aucuparia</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr"/>
@@ -1713,10 +1683,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>133315953</v>
+        <v>133315969</v>
       </c>
       <c r="B10" t="n">
-        <v>99178</v>
+        <v>79373</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1724,54 +1694,37 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K10" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="L10" t="inlineStr"/>
-      <c r="N10" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
+      <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>Erik-Nilsabodarna, Jmt</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>495579</v>
+        <v>495692</v>
       </c>
       <c r="R10" t="n">
-        <v>7037546</v>
+        <v>7037757</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1806,11 +1759,6 @@
           <t>2026-04-23</t>
         </is>
       </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Minst 7 plantor inom ca 0,5 m2 yta.</t>
-        </is>
-      </c>
       <c r="AD10" t="b">
         <v>0</v>
       </c>
@@ -1823,7 +1771,27 @@
       </c>
       <c r="AH10" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ10" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK10" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM10" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO10" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT10" t="inlineStr"/>
@@ -1841,10 +1809,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>133315945</v>
+        <v>133315970</v>
       </c>
       <c r="B11" t="n">
-        <v>99178</v>
+        <v>79373</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1852,39 +1820,26 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K11" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="L11" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
@@ -1892,10 +1847,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>495677</v>
+        <v>495669</v>
       </c>
       <c r="R11" t="n">
-        <v>7037554</v>
+        <v>7037792</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1922,17 +1877,17 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>Minst 25 plantor inom ca 1 m2 yta.</t>
+          <t>På gran i granskog.</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1947,7 +1902,22 @@
       </c>
       <c r="AH11" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ11" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK11" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO11" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT11" t="inlineStr"/>
@@ -1965,10 +1935,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>133315949</v>
+        <v>133315972</v>
       </c>
       <c r="B12" t="n">
-        <v>99178</v>
+        <v>79373</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1976,39 +1946,26 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="L12" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
@@ -2016,10 +1973,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>495648</v>
+        <v>495661</v>
       </c>
       <c r="R12" t="n">
-        <v>7037599</v>
+        <v>7037824</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -2056,7 +2013,7 @@
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>Minst 7 plantor inom ca 0,5 m2 yta.</t>
+          <t>På flera granar.</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2072,6 +2029,26 @@
       <c r="AH12" t="inlineStr">
         <is>
           <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ12" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK12" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM12" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO12" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT12" t="inlineStr"/>
@@ -2089,14 +2066,14 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>133315992</v>
+        <v>133315989</v>
       </c>
       <c r="B13" t="n">
-        <v>79358</v>
+        <v>79373</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
@@ -2127,10 +2104,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>495584</v>
+        <v>495613</v>
       </c>
       <c r="R13" t="n">
-        <v>7037513</v>
+        <v>7037684</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2165,6 +2142,11 @@
           <t>2026-04-23</t>
         </is>
       </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>På bark av tall.</t>
+        </is>
+      </c>
       <c r="AD13" t="b">
         <v>0</v>
       </c>
@@ -2182,17 +2164,22 @@
       </c>
       <c r="AJ13" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>tall</t>
         </is>
       </c>
       <c r="AK13" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AM13" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO13" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Bark on living woody plant # Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT13" t="inlineStr"/>
@@ -2210,38 +2197,37 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>133315933</v>
+        <v>133315990</v>
       </c>
       <c r="B14" t="n">
-        <v>98049</v>
+        <v>79373</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>221941</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="J14" t="inlineStr"/>
       <c r="K14" t="inlineStr"/>
-      <c r="L14" t="inlineStr"/>
       <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
@@ -2249,10 +2235,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>495612</v>
+        <v>495609</v>
       </c>
       <c r="R14" t="n">
-        <v>7037520</v>
+        <v>7037717</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2287,6 +2273,11 @@
           <t>2026-04-23</t>
         </is>
       </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>På flera granar.</t>
+        </is>
+      </c>
       <c r="AD14" t="b">
         <v>0</v>
       </c>
@@ -2302,9 +2293,24 @@
           <t>Barrskog</t>
         </is>
       </c>
-      <c r="AI14" t="inlineStr">
-        <is>
-          <t>Barrblandskog.</t>
+      <c r="AJ14" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK14" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM14" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO14" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT14" t="inlineStr"/>
@@ -2322,10 +2328,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>133315951</v>
+        <v>133315991</v>
       </c>
       <c r="B15" t="n">
-        <v>99178</v>
+        <v>79373</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2333,39 +2339,26 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K15" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="L15" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="J15" t="inlineStr"/>
+      <c r="K15" t="inlineStr"/>
       <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
@@ -2373,10 +2366,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>495631</v>
+        <v>495588</v>
       </c>
       <c r="R15" t="n">
-        <v>7037575</v>
+        <v>7037632</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2411,11 +2404,6 @@
           <t>2026-04-23</t>
         </is>
       </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>Minst 10 plantor inom ca 0,5 m2 yta.</t>
-        </is>
-      </c>
       <c r="AD15" t="b">
         <v>0</v>
       </c>
@@ -2429,6 +2417,21 @@
       <c r="AH15" t="inlineStr">
         <is>
           <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ15" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK15" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO15" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT15" t="inlineStr"/>
@@ -2446,14 +2449,14 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>133315966</v>
+        <v>133315992</v>
       </c>
       <c r="B16" t="n">
-        <v>79358</v>
+        <v>79373</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
@@ -2484,10 +2487,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>495747</v>
+        <v>495584</v>
       </c>
       <c r="R16" t="n">
-        <v>7037681</v>
+        <v>7037513</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2567,14 +2570,14 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>133315989</v>
+        <v>133315993</v>
       </c>
       <c r="B17" t="n">
-        <v>79358</v>
+        <v>79373</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E17" t="n">
@@ -2605,10 +2608,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>495613</v>
+        <v>495642</v>
       </c>
       <c r="R17" t="n">
-        <v>7037684</v>
+        <v>7037530</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2643,11 +2646,6 @@
           <t>2026-04-23</t>
         </is>
       </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>På bark av tall.</t>
-        </is>
-      </c>
       <c r="AD17" t="b">
         <v>0</v>
       </c>
@@ -2663,24 +2661,24 @@
           <t>Barrskog</t>
         </is>
       </c>
+      <c r="AI17" t="inlineStr">
+        <is>
+          <t>Barrblandskog.</t>
+        </is>
+      </c>
       <c r="AJ17" t="inlineStr">
         <is>
-          <t>tall</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK17" t="inlineStr">
         <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AM17" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO17" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Pinus sylvestris</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT17" t="inlineStr"/>
@@ -2698,65 +2696,48 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>133315957</v>
+        <v>133315934</v>
       </c>
       <c r="B18" t="n">
-        <v>99178</v>
+        <v>80488</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J18" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K18" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="L18" t="inlineStr"/>
-      <c r="N18" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="J18" t="inlineStr"/>
+      <c r="K18" t="inlineStr"/>
+      <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
           <t>Erik-Nilsabodarna, Jmt</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>495673</v>
+        <v>495732</v>
       </c>
       <c r="R18" t="n">
-        <v>7037599</v>
+        <v>7037736</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2793,7 +2774,7 @@
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>Minst 50 plantor inom ca 1,5 m2 yta i barrblandskog.</t>
+          <t>På en sälglåga.</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2808,7 +2789,27 @@
       </c>
       <c r="AH18" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ18" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK18" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM18" t="inlineStr">
+        <is>
+          <t>Bark på dött träd</t>
+        </is>
+      </c>
+      <c r="AO18" t="inlineStr">
+        <is>
+          <t>Bark of dead wood # Salix caprea</t>
         </is>
       </c>
       <c r="AT18" t="inlineStr"/>
@@ -2829,7 +2830,7 @@
         <v>133315938</v>
       </c>
       <c r="B19" t="n">
-        <v>80473</v>
+        <v>80488</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2952,65 +2953,52 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>133315947</v>
+        <v>133315939</v>
       </c>
       <c r="B20" t="n">
-        <v>99178</v>
+        <v>80488</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>33</t>
-        </is>
-      </c>
-      <c r="J20" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="J20" t="inlineStr"/>
       <c r="K20" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="L20" t="inlineStr"/>
-      <c r="N20" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>med soral</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
           <t>Erik-Nilsabodarna, Jmt</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>495698</v>
+        <v>495555</v>
       </c>
       <c r="R20" t="n">
-        <v>7037636</v>
+        <v>7037564</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -3037,17 +3025,17 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>Minst 33 plantor och 1 vinterståndare inom ca 0,5 m2 yta.</t>
+          <t>På sälg med soral.</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -3063,6 +3051,26 @@
       <c r="AH20" t="inlineStr">
         <is>
           <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ20" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK20" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM20" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO20" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT20" t="inlineStr"/>
@@ -3080,37 +3088,41 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>133315993</v>
+        <v>133315940</v>
       </c>
       <c r="B21" t="n">
-        <v>79358</v>
+        <v>80500</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6425</v>
+        <v>6464</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
       <c r="J21" t="inlineStr"/>
-      <c r="K21" t="inlineStr"/>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
@@ -3118,10 +3130,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>495642</v>
+        <v>495734</v>
       </c>
       <c r="R21" t="n">
-        <v>7037530</v>
+        <v>7037731</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -3156,6 +3168,11 @@
           <t>2026-04-23</t>
         </is>
       </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>På en rönn.</t>
+        </is>
+      </c>
       <c r="AD21" t="b">
         <v>0</v>
       </c>
@@ -3168,27 +3185,27 @@
       </c>
       <c r="AH21" t="inlineStr">
         <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AI21" t="inlineStr">
-        <is>
-          <t>Barrblandskog.</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AJ21" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>rönn</t>
         </is>
       </c>
       <c r="AK21" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Sorbus aucuparia</t>
+        </is>
+      </c>
+      <c r="AM21" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO21" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Bark on living woody plant # Sorbus aucuparia</t>
         </is>
       </c>
       <c r="AT21" t="inlineStr"/>
@@ -3206,65 +3223,52 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>133315955</v>
+        <v>133315941</v>
       </c>
       <c r="B22" t="n">
-        <v>99178</v>
+        <v>80500</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>220787</v>
+        <v>6464</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="J22" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(L.) Ach.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="J22" t="inlineStr"/>
       <c r="K22" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="L22" t="inlineStr"/>
-      <c r="N22" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>med apothecier</t>
+        </is>
+      </c>
+      <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
           <t>Erik-Nilsabodarna, Jmt</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>495605</v>
+        <v>495733</v>
       </c>
       <c r="R22" t="n">
-        <v>7037578</v>
+        <v>7037737</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3301,7 +3305,7 @@
       </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>Minst 14 plantor och 1 vinterståndare inom ca 1,5 m2 yta.</t>
+          <t>På en sälglåga.</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3317,6 +3321,26 @@
       <c r="AH22" t="inlineStr">
         <is>
           <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ22" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK22" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM22" t="inlineStr">
+        <is>
+          <t>Bark på dött träd</t>
+        </is>
+      </c>
+      <c r="AO22" t="inlineStr">
+        <is>
+          <t>Bark of dead wood # Salix caprea</t>
         </is>
       </c>
       <c r="AT22" t="inlineStr"/>
@@ -3334,10 +3358,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>133315970</v>
+        <v>133315900</v>
       </c>
       <c r="B23" t="n">
-        <v>79358</v>
+        <v>57975</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3345,26 +3369,31 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
-      <c r="J23" t="inlineStr"/>
       <c r="K23" t="inlineStr"/>
+      <c r="L23" t="inlineStr"/>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
@@ -3372,10 +3401,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>495669</v>
+        <v>495727</v>
       </c>
       <c r="R23" t="n">
-        <v>7037792</v>
+        <v>7037737</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3412,7 +3441,7 @@
       </c>
       <c r="AC23" t="inlineStr">
         <is>
-          <t>På gran i granskog.</t>
+          <t>Ringhack, äldre, på stambasen av en gran med spår av visst sav/kådaflöde.</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3421,7 +3450,6 @@
       <c r="AE23" t="b">
         <v>0</v>
       </c>
-      <c r="AF23" t="inlineStr"/>
       <c r="AG23" t="b">
         <v>0</v>
       </c>
@@ -3460,50 +3488,42 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>133315946</v>
+        <v>133315911</v>
       </c>
       <c r="B24" t="n">
-        <v>99178</v>
+        <v>57975</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
-      <c r="J24" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K24" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
+      <c r="K24" t="inlineStr"/>
       <c r="L24" t="inlineStr"/>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
@@ -3511,10 +3531,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>495707</v>
+        <v>495622</v>
       </c>
       <c r="R24" t="n">
-        <v>7037627</v>
+        <v>7037708</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3541,17 +3561,17 @@
       </c>
       <c r="Y24" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="AC24" t="inlineStr">
         <is>
-          <t>Minst 17 plantor inom ca 1,5 m2 yta.</t>
+          <t>Ringhack, färska och äldre, längs flera meter på en gran.</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3560,13 +3580,32 @@
       <c r="AE24" t="b">
         <v>0</v>
       </c>
-      <c r="AF24" t="inlineStr"/>
       <c r="AG24" t="b">
         <v>0</v>
       </c>
       <c r="AH24" t="inlineStr">
         <is>
           <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ24" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK24" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM24" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO24" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT24" t="inlineStr"/>
@@ -3584,10 +3623,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>133315962</v>
+        <v>133315912</v>
       </c>
       <c r="B25" t="n">
-        <v>79358</v>
+        <v>57975</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3595,26 +3634,31 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
-      <c r="J25" t="inlineStr"/>
       <c r="K25" t="inlineStr"/>
+      <c r="L25" t="inlineStr"/>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
@@ -3622,10 +3666,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>495710</v>
+        <v>495614</v>
       </c>
       <c r="R25" t="n">
-        <v>7037634</v>
+        <v>7037710</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3652,17 +3696,17 @@
       </c>
       <c r="Y25" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="AC25" t="inlineStr">
         <is>
-          <t>På grenar av en stående död gran och även på andra levande granar.</t>
+          <t>Ringhack, äldre, på en gran.</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3671,7 +3715,6 @@
       <c r="AE25" t="b">
         <v>0</v>
       </c>
-      <c r="AF25" t="inlineStr"/>
       <c r="AG25" t="b">
         <v>0</v>
       </c>
@@ -3690,14 +3733,9 @@
           <t>Picea abies</t>
         </is>
       </c>
-      <c r="AM25" t="inlineStr">
-        <is>
-          <t>Stående död trädstam/högstubbe</t>
-        </is>
-      </c>
       <c r="AO25" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Picea abies</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT25" t="inlineStr"/>
@@ -3715,10 +3753,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>133315968</v>
+        <v>133315913</v>
       </c>
       <c r="B26" t="n">
-        <v>79358</v>
+        <v>57975</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3726,26 +3764,31 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
-      <c r="J26" t="inlineStr"/>
       <c r="K26" t="inlineStr"/>
+      <c r="L26" t="inlineStr"/>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
@@ -3753,10 +3796,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>495723</v>
+        <v>495587</v>
       </c>
       <c r="R26" t="n">
-        <v>7037735</v>
+        <v>7037627</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3791,34 +3834,38 @@
           <t>2026-04-23</t>
         </is>
       </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>Ringhack, äldre, långt upp på en tall.</t>
+        </is>
+      </c>
       <c r="AD26" t="b">
         <v>0</v>
       </c>
       <c r="AE26" t="b">
         <v>0</v>
       </c>
-      <c r="AF26" t="inlineStr"/>
       <c r="AG26" t="b">
         <v>0</v>
       </c>
       <c r="AH26" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AJ26" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>tall</t>
         </is>
       </c>
       <c r="AK26" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AO26" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT26" t="inlineStr"/>
@@ -3836,65 +3883,53 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>133315959</v>
+        <v>133315914</v>
       </c>
       <c r="B27" t="n">
-        <v>99178</v>
+        <v>57975</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="J27" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K27" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
+      <c r="K27" t="inlineStr"/>
       <c r="L27" t="inlineStr"/>
-      <c r="N27" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
           <t>Erik-Nilsabodarna, Jmt</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>495734</v>
+        <v>495593</v>
       </c>
       <c r="R27" t="n">
-        <v>7037728</v>
+        <v>7037607</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3931,7 +3966,7 @@
       </c>
       <c r="AC27" t="inlineStr">
         <is>
-          <t>Minst 25 plantor och 2 vinterståndare inom ca 0,5 m2 yta i granskog, intill en rönn med luddlav.</t>
+          <t>Ringhack, färska, längs flera meter på en gran.</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3940,13 +3975,32 @@
       <c r="AE27" t="b">
         <v>0</v>
       </c>
-      <c r="AF27" t="inlineStr"/>
       <c r="AG27" t="b">
         <v>0</v>
       </c>
       <c r="AH27" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ27" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK27" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM27" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO27" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT27" t="inlineStr"/>
@@ -3964,10 +4018,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>133315991</v>
+        <v>133315915</v>
       </c>
       <c r="B28" t="n">
-        <v>79358</v>
+        <v>57975</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3975,26 +4029,31 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
-      <c r="J28" t="inlineStr"/>
       <c r="K28" t="inlineStr"/>
+      <c r="L28" t="inlineStr"/>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
@@ -4002,10 +4061,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>495588</v>
+        <v>495589</v>
       </c>
       <c r="R28" t="n">
-        <v>7037632</v>
+        <v>7037613</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -4040,13 +4099,17 @@
           <t>2026-04-23</t>
         </is>
       </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>Ringhack, färska, på en gran.</t>
+        </is>
+      </c>
       <c r="AD28" t="b">
         <v>0</v>
       </c>
       <c r="AE28" t="b">
         <v>0</v>
       </c>
-      <c r="AF28" t="inlineStr"/>
       <c r="AG28" t="b">
         <v>0</v>
       </c>
@@ -4065,9 +4128,14 @@
           <t>Picea abies</t>
         </is>
       </c>
+      <c r="AM28" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
       <c r="AO28" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT28" t="inlineStr"/>
@@ -4085,38 +4153,42 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>133315931</v>
+        <v>133315916</v>
       </c>
       <c r="B29" t="n">
-        <v>98043</v>
+        <v>57975</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>221945</v>
+        <v>100109</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
-      <c r="J29" t="inlineStr"/>
       <c r="K29" t="inlineStr"/>
       <c r="L29" t="inlineStr"/>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
@@ -4124,10 +4196,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>495576</v>
+        <v>495579</v>
       </c>
       <c r="R29" t="n">
-        <v>7037550</v>
+        <v>7037617</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -4162,19 +4234,38 @@
           <t>2026-04-23</t>
         </is>
       </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>Ringhack, färska och äldre, på en gran.</t>
+        </is>
+      </c>
       <c r="AD29" t="b">
         <v>0</v>
       </c>
       <c r="AE29" t="b">
         <v>0</v>
       </c>
-      <c r="AF29" t="inlineStr"/>
       <c r="AG29" t="b">
         <v>0</v>
       </c>
       <c r="AH29" t="inlineStr">
         <is>
           <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ29" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK29" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO29" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT29" t="inlineStr"/>
@@ -4192,10 +4283,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>133315964</v>
+        <v>133315917</v>
       </c>
       <c r="B30" t="n">
-        <v>79358</v>
+        <v>57975</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4203,26 +4294,31 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
-      <c r="J30" t="inlineStr"/>
       <c r="K30" t="inlineStr"/>
+      <c r="L30" t="inlineStr"/>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
@@ -4230,10 +4326,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>495652</v>
+        <v>495572</v>
       </c>
       <c r="R30" t="n">
-        <v>7037696</v>
+        <v>7037628</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -4270,7 +4366,7 @@
       </c>
       <c r="AC30" t="inlineStr">
         <is>
-          <t>På flera granar.</t>
+          <t>Ringhack, färska och äldre, på en gran.</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4279,7 +4375,6 @@
       <c r="AE30" t="b">
         <v>0</v>
       </c>
-      <c r="AF30" t="inlineStr"/>
       <c r="AG30" t="b">
         <v>0</v>
       </c>
@@ -4318,10 +4413,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>133315963</v>
+        <v>133315918</v>
       </c>
       <c r="B31" t="n">
-        <v>79358</v>
+        <v>57975</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4329,26 +4424,31 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
-      <c r="J31" t="inlineStr"/>
       <c r="K31" t="inlineStr"/>
+      <c r="L31" t="inlineStr"/>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
@@ -4356,10 +4456,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>495696</v>
+        <v>495543</v>
       </c>
       <c r="R31" t="n">
-        <v>7037705</v>
+        <v>7037573</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4396,7 +4496,7 @@
       </c>
       <c r="AC31" t="inlineStr">
         <is>
-          <t>På flera granar.</t>
+          <t>Ringhack, färska, högt upp på en gran.</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4405,7 +4505,6 @@
       <c r="AE31" t="b">
         <v>0</v>
       </c>
-      <c r="AF31" t="inlineStr"/>
       <c r="AG31" t="b">
         <v>0</v>
       </c>
@@ -4424,9 +4523,14 @@
           <t>Picea abies</t>
         </is>
       </c>
+      <c r="AM31" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
       <c r="AO31" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT31" t="inlineStr"/>
@@ -4444,65 +4548,53 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>133315952</v>
+        <v>133315919</v>
       </c>
       <c r="B32" t="n">
-        <v>99178</v>
+        <v>57975</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
-      <c r="J32" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K32" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
+      <c r="K32" t="inlineStr"/>
       <c r="L32" t="inlineStr"/>
-      <c r="N32" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
           <t>Erik-Nilsabodarna, Jmt</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>495622</v>
+        <v>495545</v>
       </c>
       <c r="R32" t="n">
-        <v>7037566</v>
+        <v>7037553</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4539,7 +4631,7 @@
       </c>
       <c r="AC32" t="inlineStr">
         <is>
-          <t>Minst 17 plantor inom ca 0,5 m2 yta.</t>
+          <t>Ringhack (savhack), färska, på en gran.</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4548,7 +4640,6 @@
       <c r="AE32" t="b">
         <v>0</v>
       </c>
-      <c r="AF32" t="inlineStr"/>
       <c r="AG32" t="b">
         <v>0</v>
       </c>
@@ -4557,9 +4648,24 @@
           <t>Barrskog</t>
         </is>
       </c>
-      <c r="AI32" t="inlineStr">
-        <is>
-          <t>Barrblandskog av gran och tall med inslag av asp, björk och sälg.</t>
+      <c r="AJ32" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK32" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM32" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO32" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT32" t="inlineStr"/>
@@ -4577,65 +4683,53 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>133315954</v>
+        <v>133315920</v>
       </c>
       <c r="B33" t="n">
-        <v>99178</v>
+        <v>57975</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="J33" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K33" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr"/>
+      <c r="K33" t="inlineStr"/>
       <c r="L33" t="inlineStr"/>
-      <c r="N33" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
           <t>Erik-Nilsabodarna, Jmt</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>495618</v>
+        <v>495547</v>
       </c>
       <c r="R33" t="n">
-        <v>7037521</v>
+        <v>7037525</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4672,7 +4766,7 @@
       </c>
       <c r="AC33" t="inlineStr">
         <is>
-          <t>Minst 15 plantor inom ca 1,5 m2 yta.</t>
+          <t>Ringhack, färska, långt upp på en tall.</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4681,13 +4775,32 @@
       <c r="AE33" t="b">
         <v>0</v>
       </c>
-      <c r="AF33" t="inlineStr"/>
       <c r="AG33" t="b">
         <v>0</v>
       </c>
       <c r="AH33" t="inlineStr">
         <is>
           <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ33" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK33" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AM33" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO33" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT33" t="inlineStr"/>
@@ -4705,50 +4818,42 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>133315956</v>
+        <v>133315921</v>
       </c>
       <c r="B34" t="n">
-        <v>99178</v>
+        <v>57975</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I34" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J34" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K34" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr"/>
+      <c r="K34" t="inlineStr"/>
       <c r="L34" t="inlineStr"/>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
@@ -4756,10 +4861,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>495665</v>
+        <v>495549</v>
       </c>
       <c r="R34" t="n">
-        <v>7037578</v>
+        <v>7037518</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4796,7 +4901,7 @@
       </c>
       <c r="AC34" t="inlineStr">
         <is>
-          <t>Minst 5 plantor inom ca 0,5 m2 yta.</t>
+          <t>Ringhack, färska, på en gran.</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4805,13 +4910,32 @@
       <c r="AE34" t="b">
         <v>0</v>
       </c>
-      <c r="AF34" t="inlineStr"/>
       <c r="AG34" t="b">
         <v>0</v>
       </c>
       <c r="AH34" t="inlineStr">
         <is>
           <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ34" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK34" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM34" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO34" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT34" t="inlineStr"/>
@@ -4829,10 +4953,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>133315990</v>
+        <v>133315922</v>
       </c>
       <c r="B35" t="n">
-        <v>79358</v>
+        <v>57975</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4840,26 +4964,31 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
-      <c r="J35" t="inlineStr"/>
       <c r="K35" t="inlineStr"/>
+      <c r="L35" t="inlineStr"/>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
@@ -4867,10 +4996,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>495609</v>
+        <v>495555</v>
       </c>
       <c r="R35" t="n">
-        <v>7037717</v>
+        <v>7037504</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4907,7 +5036,7 @@
       </c>
       <c r="AC35" t="inlineStr">
         <is>
-          <t>På flera granar.</t>
+          <t>Ringhack, färska och äldre, längs flera meter på en gran.</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4916,7 +5045,6 @@
       <c r="AE35" t="b">
         <v>0</v>
       </c>
-      <c r="AF35" t="inlineStr"/>
       <c r="AG35" t="b">
         <v>0</v>
       </c>
@@ -4925,6 +5053,11 @@
           <t>Barrskog</t>
         </is>
       </c>
+      <c r="AI35" t="inlineStr">
+        <is>
+          <t>Barrblandskog med tall och gran.</t>
+        </is>
+      </c>
       <c r="AJ35" t="inlineStr">
         <is>
           <t>gran</t>
@@ -4937,12 +5070,12 @@
       </c>
       <c r="AM35" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO35" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT35" t="inlineStr"/>
@@ -4960,65 +5093,53 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>133315958</v>
+        <v>133315923</v>
       </c>
       <c r="B36" t="n">
-        <v>99178</v>
+        <v>57975</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I36" t="inlineStr">
-        <is>
-          <t>60</t>
-        </is>
-      </c>
-      <c r="J36" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K36" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr"/>
+      <c r="K36" t="inlineStr"/>
       <c r="L36" t="inlineStr"/>
-      <c r="N36" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
           <t>Erik-Nilsabodarna, Jmt</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>495724</v>
+        <v>495568</v>
       </c>
       <c r="R36" t="n">
-        <v>7037681</v>
+        <v>7037491</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -5055,7 +5176,7 @@
       </c>
       <c r="AC36" t="inlineStr">
         <is>
-          <t>Minst 60 vitala plantor och 2 vinterståndare inom ca 2 m2 yta i  barrblandskog.</t>
+          <t>Ringhack, äldre, med kådaflöden på en gran.</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -5064,13 +5185,32 @@
       <c r="AE36" t="b">
         <v>0</v>
       </c>
-      <c r="AF36" t="inlineStr"/>
       <c r="AG36" t="b">
         <v>0</v>
       </c>
       <c r="AH36" t="inlineStr">
         <is>
           <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ36" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK36" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM36" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO36" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT36" t="inlineStr"/>
@@ -5088,10 +5228,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>133315965</v>
+        <v>133315924</v>
       </c>
       <c r="B37" t="n">
-        <v>79358</v>
+        <v>57975</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -5099,26 +5239,31 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
-      <c r="J37" t="inlineStr"/>
       <c r="K37" t="inlineStr"/>
+      <c r="L37" t="inlineStr"/>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
@@ -5126,10 +5271,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>495666</v>
+        <v>495636</v>
       </c>
       <c r="R37" t="n">
-        <v>7037645</v>
+        <v>7037503</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -5166,7 +5311,7 @@
       </c>
       <c r="AC37" t="inlineStr">
         <is>
-          <t>På flera granar.</t>
+          <t>Ringhack, äldre, enstaka högt upp på en tall.</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -5175,7 +5320,6 @@
       <c r="AE37" t="b">
         <v>0</v>
       </c>
-      <c r="AF37" t="inlineStr"/>
       <c r="AG37" t="b">
         <v>0</v>
       </c>
@@ -5184,24 +5328,24 @@
           <t>Barrskog</t>
         </is>
       </c>
-      <c r="AI37" t="inlineStr">
-        <is>
-          <t>Barrblandskog.</t>
-        </is>
-      </c>
       <c r="AJ37" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>tall</t>
         </is>
       </c>
       <c r="AK37" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AM37" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO37" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Stem on living tree # Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT37" t="inlineStr"/>
@@ -5219,42 +5363,42 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>133315900</v>
+        <v>133315943</v>
       </c>
       <c r="B38" t="n">
-        <v>57975</v>
+        <v>111153</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>100109</v>
+        <v>220240</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Linnea</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Linnaea borealis</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
-      <c r="K38" t="inlineStr"/>
+      <c r="J38" t="inlineStr"/>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="L38" t="inlineStr"/>
-      <c r="M38" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
@@ -5262,10 +5406,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>495727</v>
+        <v>495656</v>
       </c>
       <c r="R38" t="n">
-        <v>7037737</v>
+        <v>7037779</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -5300,38 +5444,19 @@
           <t>2026-04-23</t>
         </is>
       </c>
-      <c r="AC38" t="inlineStr">
-        <is>
-          <t>Ringhack, äldre, på stambasen av en gran med spår av visst sav/kådaflöde.</t>
-        </is>
-      </c>
       <c r="AD38" t="b">
         <v>0</v>
       </c>
       <c r="AE38" t="b">
         <v>0</v>
       </c>
+      <c r="AF38" t="inlineStr"/>
       <c r="AG38" t="b">
         <v>0</v>
       </c>
       <c r="AH38" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ38" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK38" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO38" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT38" t="inlineStr"/>
@@ -5349,42 +5474,50 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>133315924</v>
+        <v>133315945</v>
       </c>
       <c r="B39" t="n">
-        <v>57975</v>
+        <v>99195</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I39" t="inlineStr"/>
-      <c r="K39" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="L39" t="inlineStr"/>
-      <c r="M39" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
@@ -5392,10 +5525,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>495636</v>
+        <v>495677</v>
       </c>
       <c r="R39" t="n">
-        <v>7037503</v>
+        <v>7037554</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -5422,17 +5555,17 @@
       </c>
       <c r="Y39" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-24</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-24</t>
         </is>
       </c>
       <c r="AC39" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, enstaka högt upp på en tall.</t>
+          <t>Minst 25 plantor inom ca 1 m2 yta.</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -5441,32 +5574,13 @@
       <c r="AE39" t="b">
         <v>0</v>
       </c>
+      <c r="AF39" t="inlineStr"/>
       <c r="AG39" t="b">
         <v>0</v>
       </c>
       <c r="AH39" t="inlineStr">
         <is>
           <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ39" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK39" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AM39" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO39" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT39" t="inlineStr"/>
@@ -5484,42 +5598,50 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>133315921</v>
+        <v>133315946</v>
       </c>
       <c r="B40" t="n">
-        <v>57975</v>
+        <v>99195</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I40" t="inlineStr"/>
-      <c r="K40" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="L40" t="inlineStr"/>
-      <c r="M40" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
@@ -5527,10 +5649,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>495549</v>
+        <v>495707</v>
       </c>
       <c r="R40" t="n">
-        <v>7037518</v>
+        <v>7037627</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -5557,17 +5679,17 @@
       </c>
       <c r="Y40" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-24</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-24</t>
         </is>
       </c>
       <c r="AC40" t="inlineStr">
         <is>
-          <t>Ringhack, färska, på en gran.</t>
+          <t>Minst 17 plantor inom ca 1,5 m2 yta.</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5576,32 +5698,13 @@
       <c r="AE40" t="b">
         <v>0</v>
       </c>
+      <c r="AF40" t="inlineStr"/>
       <c r="AG40" t="b">
         <v>0</v>
       </c>
       <c r="AH40" t="inlineStr">
         <is>
           <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ40" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK40" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM40" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO40" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT40" t="inlineStr"/>
@@ -5619,53 +5722,65 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>133315916</v>
+        <v>133315947</v>
       </c>
       <c r="B41" t="n">
-        <v>57975</v>
+        <v>99195</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I41" t="inlineStr"/>
-      <c r="K41" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="L41" t="inlineStr"/>
-      <c r="M41" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N41" t="inlineStr"/>
+      <c r="N41" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P41" t="inlineStr">
         <is>
           <t>Erik-Nilsabodarna, Jmt</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>495579</v>
+        <v>495698</v>
       </c>
       <c r="R41" t="n">
-        <v>7037617</v>
+        <v>7037636</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5692,17 +5807,17 @@
       </c>
       <c r="Y41" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-24</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-24</t>
         </is>
       </c>
       <c r="AC41" t="inlineStr">
         <is>
-          <t>Ringhack, färska och äldre, på en gran.</t>
+          <t>Minst 33 plantor och 1 vinterståndare inom ca 0,5 m2 yta.</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5711,27 +5826,13 @@
       <c r="AE41" t="b">
         <v>0</v>
       </c>
+      <c r="AF41" t="inlineStr"/>
       <c r="AG41" t="b">
         <v>0</v>
       </c>
       <c r="AH41" t="inlineStr">
         <is>
           <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ41" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK41" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO41" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT41" t="inlineStr"/>
@@ -5749,42 +5850,50 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>133315917</v>
+        <v>133315948</v>
       </c>
       <c r="B42" t="n">
-        <v>57975</v>
+        <v>99195</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I42" t="inlineStr"/>
-      <c r="K42" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="L42" t="inlineStr"/>
-      <c r="M42" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
@@ -5792,10 +5901,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>495572</v>
+        <v>495621</v>
       </c>
       <c r="R42" t="n">
-        <v>7037628</v>
+        <v>7037632</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5832,7 +5941,7 @@
       </c>
       <c r="AC42" t="inlineStr">
         <is>
-          <t>Ringhack, färska och äldre, på en gran.</t>
+          <t>Minst 4 plantor inom ca 0,5 m2 yta.</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5841,27 +5950,13 @@
       <c r="AE42" t="b">
         <v>0</v>
       </c>
+      <c r="AF42" t="inlineStr"/>
       <c r="AG42" t="b">
         <v>0</v>
       </c>
       <c r="AH42" t="inlineStr">
         <is>
           <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ42" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK42" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO42" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT42" t="inlineStr"/>
@@ -5879,42 +5974,50 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>133315914</v>
+        <v>133315949</v>
       </c>
       <c r="B43" t="n">
-        <v>57975</v>
+        <v>99195</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I43" t="inlineStr"/>
-      <c r="K43" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="L43" t="inlineStr"/>
-      <c r="M43" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
@@ -5922,10 +6025,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>495593</v>
+        <v>495648</v>
       </c>
       <c r="R43" t="n">
-        <v>7037607</v>
+        <v>7037599</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5962,7 +6065,7 @@
       </c>
       <c r="AC43" t="inlineStr">
         <is>
-          <t>Ringhack, färska, längs flera meter på en gran.</t>
+          <t>Minst 7 plantor inom ca 0,5 m2 yta.</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5971,32 +6074,13 @@
       <c r="AE43" t="b">
         <v>0</v>
       </c>
+      <c r="AF43" t="inlineStr"/>
       <c r="AG43" t="b">
         <v>0</v>
       </c>
       <c r="AH43" t="inlineStr">
         <is>
           <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ43" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK43" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM43" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO43" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT43" t="inlineStr"/>
@@ -6014,42 +6098,50 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>133315913</v>
+        <v>133315951</v>
       </c>
       <c r="B44" t="n">
-        <v>57975</v>
+        <v>99195</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I44" t="inlineStr"/>
-      <c r="K44" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="L44" t="inlineStr"/>
-      <c r="M44" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
@@ -6057,10 +6149,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>495587</v>
+        <v>495631</v>
       </c>
       <c r="R44" t="n">
-        <v>7037627</v>
+        <v>7037575</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -6097,7 +6189,7 @@
       </c>
       <c r="AC44" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, långt upp på en tall.</t>
+          <t>Minst 10 plantor inom ca 0,5 m2 yta.</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -6106,27 +6198,13 @@
       <c r="AE44" t="b">
         <v>0</v>
       </c>
+      <c r="AF44" t="inlineStr"/>
       <c r="AG44" t="b">
         <v>0</v>
       </c>
       <c r="AH44" t="inlineStr">
         <is>
           <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ44" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK44" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO44" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT44" t="inlineStr"/>
@@ -6144,53 +6222,65 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>133315923</v>
+        <v>133315952</v>
       </c>
       <c r="B45" t="n">
-        <v>57975</v>
+        <v>99195</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I45" t="inlineStr"/>
-      <c r="K45" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="L45" t="inlineStr"/>
-      <c r="M45" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N45" t="inlineStr"/>
+      <c r="N45" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P45" t="inlineStr">
         <is>
           <t>Erik-Nilsabodarna, Jmt</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>495568</v>
+        <v>495622</v>
       </c>
       <c r="R45" t="n">
-        <v>7037491</v>
+        <v>7037566</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -6227,7 +6317,7 @@
       </c>
       <c r="AC45" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, med kådaflöden på en gran.</t>
+          <t>Minst 17 plantor inom ca 0,5 m2 yta.</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -6236,6 +6326,7 @@
       <c r="AE45" t="b">
         <v>0</v>
       </c>
+      <c r="AF45" t="inlineStr"/>
       <c r="AG45" t="b">
         <v>0</v>
       </c>
@@ -6244,24 +6335,9 @@
           <t>Barrskog</t>
         </is>
       </c>
-      <c r="AJ45" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK45" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM45" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO45" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
+      <c r="AI45" t="inlineStr">
+        <is>
+          <t>Barrblandskog av gran och tall med inslag av asp, björk och sälg.</t>
         </is>
       </c>
       <c r="AT45" t="inlineStr"/>
@@ -6279,53 +6355,65 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>133315918</v>
+        <v>133315953</v>
       </c>
       <c r="B46" t="n">
-        <v>57975</v>
+        <v>99195</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I46" t="inlineStr"/>
-      <c r="K46" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="L46" t="inlineStr"/>
-      <c r="M46" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N46" t="inlineStr"/>
+      <c r="N46" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P46" t="inlineStr">
         <is>
           <t>Erik-Nilsabodarna, Jmt</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>495543</v>
+        <v>495579</v>
       </c>
       <c r="R46" t="n">
-        <v>7037573</v>
+        <v>7037546</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -6362,7 +6450,7 @@
       </c>
       <c r="AC46" t="inlineStr">
         <is>
-          <t>Ringhack, färska, högt upp på en gran.</t>
+          <t>Minst 7 plantor inom ca 0,5 m2 yta.</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -6371,32 +6459,13 @@
       <c r="AE46" t="b">
         <v>0</v>
       </c>
+      <c r="AF46" t="inlineStr"/>
       <c r="AG46" t="b">
         <v>0</v>
       </c>
       <c r="AH46" t="inlineStr">
         <is>
           <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ46" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK46" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM46" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO46" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT46" t="inlineStr"/>
@@ -6414,53 +6483,65 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>133315912</v>
+        <v>133315954</v>
       </c>
       <c r="B47" t="n">
-        <v>57975</v>
+        <v>99195</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I47" t="inlineStr"/>
-      <c r="K47" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="L47" t="inlineStr"/>
-      <c r="M47" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N47" t="inlineStr"/>
+      <c r="N47" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P47" t="inlineStr">
         <is>
           <t>Erik-Nilsabodarna, Jmt</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>495614</v>
+        <v>495618</v>
       </c>
       <c r="R47" t="n">
-        <v>7037710</v>
+        <v>7037521</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -6497,7 +6578,7 @@
       </c>
       <c r="AC47" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, på en gran.</t>
+          <t>Minst 15 plantor inom ca 1,5 m2 yta.</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -6506,27 +6587,13 @@
       <c r="AE47" t="b">
         <v>0</v>
       </c>
+      <c r="AF47" t="inlineStr"/>
       <c r="AG47" t="b">
         <v>0</v>
       </c>
       <c r="AH47" t="inlineStr">
         <is>
           <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ47" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK47" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO47" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT47" t="inlineStr"/>
@@ -6544,53 +6611,65 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>133315922</v>
+        <v>133315955</v>
       </c>
       <c r="B48" t="n">
-        <v>57975</v>
+        <v>99195</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I48" t="inlineStr"/>
-      <c r="K48" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="L48" t="inlineStr"/>
-      <c r="M48" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N48" t="inlineStr"/>
+      <c r="N48" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P48" t="inlineStr">
         <is>
           <t>Erik-Nilsabodarna, Jmt</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>495555</v>
+        <v>495605</v>
       </c>
       <c r="R48" t="n">
-        <v>7037504</v>
+        <v>7037578</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -6627,7 +6706,7 @@
       </c>
       <c r="AC48" t="inlineStr">
         <is>
-          <t>Ringhack, färska och äldre, längs flera meter på en gran.</t>
+          <t>Minst 14 plantor och 1 vinterståndare inom ca 1,5 m2 yta.</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -6636,37 +6715,13 @@
       <c r="AE48" t="b">
         <v>0</v>
       </c>
+      <c r="AF48" t="inlineStr"/>
       <c r="AG48" t="b">
         <v>0</v>
       </c>
       <c r="AH48" t="inlineStr">
         <is>
           <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AI48" t="inlineStr">
-        <is>
-          <t>Barrblandskog med tall och gran.</t>
-        </is>
-      </c>
-      <c r="AJ48" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK48" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM48" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO48" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT48" t="inlineStr"/>
@@ -6684,42 +6739,50 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>133315919</v>
+        <v>133315956</v>
       </c>
       <c r="B49" t="n">
-        <v>57975</v>
+        <v>99195</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I49" t="inlineStr"/>
-      <c r="K49" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="L49" t="inlineStr"/>
-      <c r="M49" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
@@ -6727,10 +6790,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>495545</v>
+        <v>495665</v>
       </c>
       <c r="R49" t="n">
-        <v>7037553</v>
+        <v>7037578</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -6767,7 +6830,7 @@
       </c>
       <c r="AC49" t="inlineStr">
         <is>
-          <t>Ringhack (savhack), färska, på en gran.</t>
+          <t>Minst 5 plantor inom ca 0,5 m2 yta.</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6776,32 +6839,13 @@
       <c r="AE49" t="b">
         <v>0</v>
       </c>
+      <c r="AF49" t="inlineStr"/>
       <c r="AG49" t="b">
         <v>0</v>
       </c>
       <c r="AH49" t="inlineStr">
         <is>
           <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ49" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK49" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM49" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO49" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT49" t="inlineStr"/>
@@ -6819,53 +6863,65 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>133315915</v>
+        <v>133315957</v>
       </c>
       <c r="B50" t="n">
-        <v>57975</v>
+        <v>99195</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I50" t="inlineStr"/>
-      <c r="K50" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K50" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="L50" t="inlineStr"/>
-      <c r="M50" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N50" t="inlineStr"/>
+      <c r="N50" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P50" t="inlineStr">
         <is>
           <t>Erik-Nilsabodarna, Jmt</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>495589</v>
+        <v>495673</v>
       </c>
       <c r="R50" t="n">
-        <v>7037613</v>
+        <v>7037599</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -6902,7 +6958,7 @@
       </c>
       <c r="AC50" t="inlineStr">
         <is>
-          <t>Ringhack, färska, på en gran.</t>
+          <t>Minst 50 plantor inom ca 1,5 m2 yta i barrblandskog.</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6911,32 +6967,13 @@
       <c r="AE50" t="b">
         <v>0</v>
       </c>
+      <c r="AF50" t="inlineStr"/>
       <c r="AG50" t="b">
         <v>0</v>
       </c>
       <c r="AH50" t="inlineStr">
         <is>
           <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ50" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK50" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM50" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO50" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT50" t="inlineStr"/>
@@ -6954,53 +6991,65 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>133315911</v>
+        <v>133315958</v>
       </c>
       <c r="B51" t="n">
-        <v>57975</v>
+        <v>99195</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I51" t="inlineStr"/>
-      <c r="K51" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K51" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="L51" t="inlineStr"/>
-      <c r="M51" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N51" t="inlineStr"/>
+      <c r="N51" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P51" t="inlineStr">
         <is>
           <t>Erik-Nilsabodarna, Jmt</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>495622</v>
+        <v>495724</v>
       </c>
       <c r="R51" t="n">
-        <v>7037708</v>
+        <v>7037681</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -7037,7 +7086,7 @@
       </c>
       <c r="AC51" t="inlineStr">
         <is>
-          <t>Ringhack, färska och äldre, längs flera meter på en gran.</t>
+          <t>Minst 60 vitala plantor och 2 vinterståndare inom ca 2 m2 yta i  barrblandskog.</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -7046,32 +7095,13 @@
       <c r="AE51" t="b">
         <v>0</v>
       </c>
+      <c r="AF51" t="inlineStr"/>
       <c r="AG51" t="b">
         <v>0</v>
       </c>
       <c r="AH51" t="inlineStr">
         <is>
           <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ51" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK51" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM51" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO51" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT51" t="inlineStr"/>
@@ -7089,53 +7119,65 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>133315920</v>
+        <v>133315959</v>
       </c>
       <c r="B52" t="n">
-        <v>57975</v>
+        <v>99195</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I52" t="inlineStr"/>
-      <c r="K52" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K52" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="L52" t="inlineStr"/>
-      <c r="M52" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N52" t="inlineStr"/>
+      <c r="N52" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P52" t="inlineStr">
         <is>
           <t>Erik-Nilsabodarna, Jmt</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>495547</v>
+        <v>495734</v>
       </c>
       <c r="R52" t="n">
-        <v>7037525</v>
+        <v>7037728</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -7172,7 +7214,7 @@
       </c>
       <c r="AC52" t="inlineStr">
         <is>
-          <t>Ringhack, färska, långt upp på en tall.</t>
+          <t>Minst 25 plantor och 2 vinterståndare inom ca 0,5 m2 yta i granskog, intill en rönn med luddlav.</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -7181,32 +7223,13 @@
       <c r="AE52" t="b">
         <v>0</v>
       </c>
+      <c r="AF52" t="inlineStr"/>
       <c r="AG52" t="b">
         <v>0</v>
       </c>
       <c r="AH52" t="inlineStr">
         <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ52" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK52" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AM52" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO52" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Pinus sylvestris</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AT52" t="inlineStr"/>
@@ -7221,6 +7244,225 @@
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
+    </row>
+    <row r="53">
+      <c r="A53" t="n">
+        <v>133315933</v>
+      </c>
+      <c r="B53" t="n">
+        <v>98066</v>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E53" t="n">
+        <v>221941</v>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>Plattlummer</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>Lycopodium complanatum</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr"/>
+      <c r="J53" t="inlineStr"/>
+      <c r="K53" t="inlineStr"/>
+      <c r="L53" t="inlineStr"/>
+      <c r="N53" t="inlineStr"/>
+      <c r="P53" t="inlineStr">
+        <is>
+          <t>Erik-Nilsabodarna, Jmt</t>
+        </is>
+      </c>
+      <c r="Q53" t="n">
+        <v>495612</v>
+      </c>
+      <c r="R53" t="n">
+        <v>7037520</v>
+      </c>
+      <c r="S53" t="n">
+        <v>10</v>
+      </c>
+      <c r="T53" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U53" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V53" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W53" t="inlineStr">
+        <is>
+          <t>Häggenås</t>
+        </is>
+      </c>
+      <c r="Y53" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="AA53" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="AD53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF53" t="inlineStr"/>
+      <c r="AG53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH53" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AI53" t="inlineStr">
+        <is>
+          <t>Barrblandskog.</t>
+        </is>
+      </c>
+      <c r="AT53" t="inlineStr"/>
+      <c r="AW53" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX53" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY53" t="inlineStr"/>
+    </row>
+    <row r="54">
+      <c r="A54" t="n">
+        <v>133315931</v>
+      </c>
+      <c r="B54" t="n">
+        <v>98060</v>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E54" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr"/>
+      <c r="J54" t="inlineStr"/>
+      <c r="K54" t="inlineStr"/>
+      <c r="L54" t="inlineStr"/>
+      <c r="N54" t="inlineStr"/>
+      <c r="P54" t="inlineStr">
+        <is>
+          <t>Erik-Nilsabodarna, Jmt</t>
+        </is>
+      </c>
+      <c r="Q54" t="n">
+        <v>495576</v>
+      </c>
+      <c r="R54" t="n">
+        <v>7037550</v>
+      </c>
+      <c r="S54" t="n">
+        <v>10</v>
+      </c>
+      <c r="T54" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U54" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V54" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W54" t="inlineStr">
+        <is>
+          <t>Häggenås</t>
+        </is>
+      </c>
+      <c r="Y54" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="AA54" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="AD54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF54" t="inlineStr"/>
+      <c r="AG54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH54" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AT54" t="inlineStr"/>
+      <c r="AW54" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX54" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY54" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 17267-2026 artfynd.xlsx
+++ b/artfynd/A 17267-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY54"/>
+  <dimension ref="A1:AZ54"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -670,6 +670,11 @@
       <c r="AY1" t="inlineStr">
         <is>
           <t>Projektnamn</t>
+        </is>
+      </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
         </is>
       </c>
     </row>
@@ -793,6 +798,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133315961</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -924,6 +934,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133315962</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1050,6 +1065,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133315963</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1176,6 +1196,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133315964</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1307,6 +1332,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133315965</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1428,6 +1458,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133315966</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1559,6 +1594,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133315967</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1680,6 +1720,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133315968</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1806,6 +1851,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133315969</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1932,6 +1982,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133315970</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -2063,6 +2118,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133315972</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -2194,6 +2254,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133315989</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2325,6 +2390,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133315990</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2446,6 +2516,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133315991</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2567,6 +2642,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133315992</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2693,6 +2773,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133315993</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2824,6 +2909,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133315934</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2950,6 +3040,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133315938</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -3085,6 +3180,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133315939</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -3220,6 +3320,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133315940</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -3355,6 +3460,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133315941</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -3485,6 +3595,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133315900</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3620,6 +3735,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133315911</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3750,6 +3870,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133315912</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3880,6 +4005,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133315913</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -4015,6 +4145,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133315914</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -4150,6 +4285,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133315915</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -4280,6 +4420,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133315916</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -4410,6 +4555,11 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133315917</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -4545,6 +4695,11 @@
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133315918</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -4680,6 +4835,11 @@
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133315919</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -4815,6 +4975,11 @@
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133315920</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -4950,6 +5115,11 @@
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133315921</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -5090,6 +5260,11 @@
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133315922</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -5225,6 +5400,11 @@
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133315923</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -5360,6 +5540,11 @@
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133315924</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -5471,6 +5656,11 @@
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133315943</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -5595,6 +5785,11 @@
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133315945</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -5719,6 +5914,11 @@
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133315946</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -5847,6 +6047,11 @@
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133315947</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -5971,6 +6176,11 @@
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
+      <c r="AZ42" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133315948</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -6095,6 +6305,11 @@
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
+      <c r="AZ43" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133315949</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -6219,6 +6434,11 @@
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
+      <c r="AZ44" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133315951</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -6352,6 +6572,11 @@
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
+      <c r="AZ45" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133315952</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -6480,6 +6705,11 @@
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
+      <c r="AZ46" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133315953</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -6608,6 +6838,11 @@
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
+      <c r="AZ47" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133315954</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -6736,6 +6971,11 @@
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
+      <c r="AZ48" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133315955</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -6860,6 +7100,11 @@
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
+      <c r="AZ49" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133315956</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -6988,6 +7233,11 @@
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
+      <c r="AZ50" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133315957</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
@@ -7116,6 +7366,11 @@
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
+      <c r="AZ51" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133315958</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
@@ -7244,6 +7499,11 @@
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
+      <c r="AZ52" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133315959</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
@@ -7356,6 +7616,11 @@
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
+      <c r="AZ53" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133315933</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
@@ -7463,8 +7728,68 @@
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
+      <c r="AZ54" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133315931</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ44" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ45" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ46" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ47" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ48" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ49" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ50" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ51" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ52" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ53" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ54" r:id="rId53"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>